--- a/docentes/Cruz Alejo José Armando - Estadisticos 20241.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,183 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ABREGO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TOLENTINO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>TENCHIPE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CORREA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>SULU ALAN</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ESTRELLA ESMERALDA</t>
-  </si>
-  <si>
-    <t>ESTRELLA RUBI</t>
-  </si>
-  <si>
-    <t>XOCHITL ALELI</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>DORIAN ALEXANDER</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>KEVIN IVAN</t>
-  </si>
-  <si>
-    <t>KEIRA</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>KENYA MARIANA</t>
-  </si>
-  <si>
-    <t>LEONARDO GABRIEL</t>
-  </si>
-  <si>
-    <t>SALMA JANET</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>VICTOR JESUS</t>
-  </si>
-  <si>
-    <t>ELIUD EDUARDO</t>
-  </si>
-  <si>
-    <t>KAORY AYELEN</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>HUGO ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
   </si>
 </sst>
 </file>
@@ -703,16 +526,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H4">
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -791,16 +617,19 @@
         <v>24</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>95.83</v>
+      </c>
+      <c r="H2">
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -814,16 +643,19 @@
         <v>36</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>36</v>
       </c>
-      <c r="E3">
-        <v>36</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -837,16 +669,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H4">
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -860,16 +695,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>94.59</v>
+      </c>
+      <c r="H5">
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -925,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -960,7 +798,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -974,16 +812,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>92.86</v>
+      </c>
+      <c r="H4">
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1019,7 +860,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1049,581 +890,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920151</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920152</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>23330051920153</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>23330051920155</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>23330051920154</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920325</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920250</v>
-      </c>
-      <c r="B8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920157</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920158</v>
-      </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920159</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920161</v>
-      </c>
-      <c r="B12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920162</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920163</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920297</v>
-      </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920165</v>
-      </c>
-      <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920166</v>
-      </c>
-      <c r="B17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920167</v>
-      </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920310</v>
-      </c>
-      <c r="B19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920169</v>
-      </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920354</v>
-      </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" t="s">
-        <v>72</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920170</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920173</v>
-      </c>
-      <c r="B23" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" t="s">
-        <v>74</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920172</v>
-      </c>
-      <c r="B24" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" t="s">
-        <v>75</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920311</v>
-      </c>
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" t="s">
-        <v>76</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920174</v>
-      </c>
-      <c r="B26" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D26" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>11</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20241.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
+    <t>VOTE</t>
+  </si>
+  <si>
+    <t>CAMILO</t>
   </si>
 </sst>
 </file>
@@ -860,7 +869,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -890,6 +899,29 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330061460232</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20241.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,10 +76,19 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>COLMENARES</t>
+  </si>
+  <si>
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>VOTE</t>
+  </si>
+  <si>
+    <t>JULIO EDUARDO</t>
   </si>
   <si>
     <t>CAMILO</t>
@@ -869,7 +878,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -901,16 +910,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330061460232</v>
+        <v>22330051920424</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -920,6 +929,29 @@
       </c>
       <c r="G2">
         <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330061460232</v>
+      </c>
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20241.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -76,16 +76,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>TELLO</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
     <t>COLMENARES</t>
   </si>
   <si>
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>VOTE</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
   </si>
   <si>
     <t>JULIO EDUARDO</t>
@@ -878,7 +893,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -910,47 +925,93 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920424</v>
+        <v>23330051920022</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330061460232</v>
+        <v>23330051920313</v>
       </c>
       <c r="B3" t="s">
         <v>20</v>
       </c>
       <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920424</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330061460232</v>
+      </c>
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
         <v>12</v>
       </c>
-      <c r="G3">
+      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20241.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,39 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>TELLO</t>
-  </si>
-  <si>
-    <t>VIVANCO</t>
-  </si>
-  <si>
-    <t>COLMENARES</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>VOTE</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>LUIS AARON</t>
-  </si>
-  <si>
-    <t>JULIO EDUARDO</t>
-  </si>
-  <si>
-    <t>CAMILO</t>
   </si>
 </sst>
 </file>
@@ -796,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -831,7 +798,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -848,16 +815,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G4">
-        <v>92.86</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -874,16 +841,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G5">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -893,7 +860,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -923,98 +890,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920022</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>23330051920313</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920424</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330061460232</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
